--- a/cardapio.xlsx
+++ b/cardapio.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="85">
   <si>
     <t>Pão, hambúrguer, presunto, queijo, bacon, calabresa, ovo frito, frango, coração, alface, tomate, milho, ervilha, batata palha</t>
   </si>
@@ -71,12 +71,6 @@
     <t>Pão, confete, chocolate, leite condensado, cobertura</t>
   </si>
   <si>
-    <t>Extra</t>
-  </si>
-  <si>
-    <t>Simples</t>
-  </si>
-  <si>
     <t>Pão prensado, queijo, maionese, calabresa, hambúrguer, coração, frango, batata frita, anel de cebola, aipim, polenta, ovinho, azeitona, pepino</t>
   </si>
   <si>
@@ -86,27 +80,6 @@
     <t>Pão grande, 4 hambúrgueres, 4 queijos, 4 presuntos, calabresa, bacon, coração, frango, ovinho, pepino, milho, ervilha, alface, tomate, batata palha</t>
   </si>
   <si>
-    <t>Refrigerante</t>
-  </si>
-  <si>
-    <t>Energético</t>
-  </si>
-  <si>
-    <t>Água</t>
-  </si>
-  <si>
-    <t>Suco</t>
-  </si>
-  <si>
-    <t>Cerveja</t>
-  </si>
-  <si>
-    <t>Chopp</t>
-  </si>
-  <si>
-    <t>Dose</t>
-  </si>
-  <si>
     <t>LANCHES SALGADOS</t>
   </si>
   <si>
@@ -218,94 +191,94 @@
     <t>item</t>
   </si>
   <si>
+    <t>Big-American (X da casa)</t>
+  </si>
+  <si>
+    <t>X-Egg</t>
+  </si>
+  <si>
+    <t>Coca Cola (2 Litros)</t>
+  </si>
+  <si>
+    <t>Pepsi 2 (2 Litros)</t>
+  </si>
+  <si>
+    <t>Guaraná (2 Litros)</t>
+  </si>
+  <si>
+    <t>Sukita Uva/Laranja (2 Litros)</t>
+  </si>
+  <si>
+    <t>Sprite Limão (2 Litros)</t>
+  </si>
+  <si>
+    <t>Coca Cola (600 ml)</t>
+  </si>
+  <si>
+    <t>Guaraná (600 ml)</t>
+  </si>
+  <si>
+    <t>Energético Monster (Latão)</t>
+  </si>
+  <si>
+    <t>Coca Cola (Lata)</t>
+  </si>
+  <si>
+    <t>Guaraná (Lata)</t>
+  </si>
+  <si>
+    <t>Chopp Pilsen (500 ml)</t>
+  </si>
+  <si>
+    <t>Brahma (Lata)</t>
+  </si>
+  <si>
+    <t>Antarctica (Lata)</t>
+  </si>
+  <si>
+    <t>Schin (Lata)</t>
+  </si>
+  <si>
+    <t>Red Label (Dose)</t>
+  </si>
+  <si>
+    <t>Dreher (Dose)</t>
+  </si>
+  <si>
+    <t>Calabresa</t>
+  </si>
+  <si>
+    <t>Bacon</t>
+  </si>
+  <si>
+    <t>Coração</t>
+  </si>
+  <si>
+    <t>Frango</t>
+  </si>
+  <si>
+    <t>Cheddar</t>
+  </si>
+  <si>
+    <t>Acebolado</t>
+  </si>
+  <si>
+    <t>Picles</t>
+  </si>
+  <si>
+    <t>Ovinho Conserva</t>
+  </si>
+  <si>
+    <t>Batata Frita Extra</t>
+  </si>
+  <si>
+    <t>Maionese caseira</t>
+  </si>
+  <si>
+    <t>ingredientes</t>
+  </si>
+  <si>
     <t>preco</t>
-  </si>
-  <si>
-    <t>Big-American (X da casa)</t>
-  </si>
-  <si>
-    <t>X-Egg</t>
-  </si>
-  <si>
-    <t>Coca Cola (2 Litros)</t>
-  </si>
-  <si>
-    <t>Pepsi 2 (2 Litros)</t>
-  </si>
-  <si>
-    <t>Guaraná (2 Litros)</t>
-  </si>
-  <si>
-    <t>Sukita Uva/Laranja (2 Litros)</t>
-  </si>
-  <si>
-    <t>Sprite Limão (2 Litros)</t>
-  </si>
-  <si>
-    <t>Coca Cola (600 ml)</t>
-  </si>
-  <si>
-    <t>Guaraná (600 ml)</t>
-  </si>
-  <si>
-    <t>Energético Monster (Latão)</t>
-  </si>
-  <si>
-    <t>Coca Cola (Lata)</t>
-  </si>
-  <si>
-    <t>Guaraná (Lata)</t>
-  </si>
-  <si>
-    <t>Chopp Pilsen (500 ml)</t>
-  </si>
-  <si>
-    <t>Brahma (Lata)</t>
-  </si>
-  <si>
-    <t>Antarctica (Lata)</t>
-  </si>
-  <si>
-    <t>Schin (Lata)</t>
-  </si>
-  <si>
-    <t>Red Label (Dose)</t>
-  </si>
-  <si>
-    <t>Dreher (Dose)</t>
-  </si>
-  <si>
-    <t>Calabresa</t>
-  </si>
-  <si>
-    <t>Bacon</t>
-  </si>
-  <si>
-    <t>Coração</t>
-  </si>
-  <si>
-    <t>Frango</t>
-  </si>
-  <si>
-    <t>Cheddar</t>
-  </si>
-  <si>
-    <t>Acebolado</t>
-  </si>
-  <si>
-    <t>Picles</t>
-  </si>
-  <si>
-    <t>Ovinho Conserva</t>
-  </si>
-  <si>
-    <t>Batata Frita Extra</t>
-  </si>
-  <si>
-    <t>Maionese caseira</t>
-  </si>
-  <si>
-    <t>ingredientes</t>
   </si>
 </sst>
 </file>
@@ -454,6 +427,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -477,9 +453,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -772,36 +745,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="C1" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>93</v>
+      <c r="C1" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B2" s="2"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="B4" s="15" t="s">
-        <v>27</v>
+      <c r="B4" s="16" t="s">
+        <v>18</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D4" s="5">
         <v>32</v>
@@ -811,9 +784,9 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B5" s="15"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D5" s="5">
         <v>30</v>
@@ -823,9 +796,9 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B6" s="15"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D6" s="5">
         <v>26</v>
@@ -835,9 +808,9 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="15"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="5" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D7" s="5">
         <v>26</v>
@@ -847,9 +820,9 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B8" s="15"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D8" s="5">
         <v>26</v>
@@ -859,9 +832,9 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B9" s="15"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D9" s="5">
         <v>29</v>
@@ -871,9 +844,9 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B10" s="15"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="5" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D10" s="5">
         <v>28</v>
@@ -883,9 +856,9 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="15"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="5" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D11" s="5">
         <v>25</v>
@@ -895,9 +868,9 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="15"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="5" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D12" s="5">
         <v>26</v>
@@ -907,9 +880,9 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="15"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D13" s="5">
         <v>15</v>
@@ -919,9 +892,9 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="15"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="5" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D14" s="5">
         <v>19</v>
@@ -931,9 +904,9 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B15" s="15"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D15" s="5">
         <v>21</v>
@@ -951,11 +924,11 @@
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B17" s="15" t="s">
-        <v>28</v>
+      <c r="B17" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D17" s="5">
         <v>21</v>
@@ -965,9 +938,9 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B18" s="15"/>
+      <c r="B18" s="16"/>
       <c r="C18" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D18" s="5">
         <v>19</v>
@@ -977,9 +950,9 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B19" s="15"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="5" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D19" s="5">
         <v>19</v>
@@ -1010,23 +983,21 @@
       <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="8" t="s">
-        <v>30</v>
+      <c r="B31" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D31" s="5">
         <v>25</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>16</v>
-      </c>
+      <c r="E31" s="5"/>
     </row>
     <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B32" s="9"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D32" s="5">
         <v>32</v>
@@ -1034,9 +1005,9 @@
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B33" s="9"/>
+      <c r="B33" s="10"/>
       <c r="C33" s="5" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D33" s="5">
         <v>32</v>
@@ -1044,9 +1015,9 @@
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B34" s="9"/>
+      <c r="B34" s="10"/>
       <c r="C34" s="5" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D34" s="5">
         <v>30</v>
@@ -1054,9 +1025,9 @@
       <c r="E34" s="5"/>
     </row>
     <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B35" s="9"/>
+      <c r="B35" s="10"/>
       <c r="C35" s="5" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D35" s="5">
         <v>33</v>
@@ -1064,9 +1035,9 @@
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B36" s="9"/>
+      <c r="B36" s="10"/>
       <c r="C36" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D36" s="5">
         <v>30</v>
@@ -1074,9 +1045,9 @@
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="9"/>
+      <c r="B37" s="10"/>
       <c r="C37" s="5" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D37" s="5">
         <v>29</v>
@@ -1085,9 +1056,9 @@
     </row>
     <row r="38" spans="1:6" ht="33.75" x14ac:dyDescent="0.5">
       <c r="A38" s="2"/>
-      <c r="B38" s="10"/>
+      <c r="B38" s="11"/>
       <c r="C38" s="5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D38" s="5">
         <v>25</v>
@@ -1096,190 +1067,166 @@
       <c r="F38" s="2"/>
     </row>
     <row r="39" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="B39" s="8" t="s">
-        <v>31</v>
+      <c r="B39" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D39" s="5">
         <v>99</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="9"/>
+      <c r="B40" s="10"/>
       <c r="C40" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D40" s="5">
         <v>69</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="10"/>
+      <c r="B41" s="11"/>
       <c r="C41" s="5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D41" s="5">
         <v>96</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
-      <c r="B42" s="8" t="s">
-        <v>32</v>
+      <c r="B42" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D42" s="5">
         <v>16</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="E42" s="5"/>
       <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B43" s="9"/>
+      <c r="B43" s="10"/>
       <c r="C43" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D43" s="5">
         <v>13</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B44" s="9"/>
+      <c r="B44" s="10"/>
       <c r="C44" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D44" s="5">
         <v>13</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B45" s="9"/>
+      <c r="B45" s="10"/>
       <c r="C45" s="5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D45" s="5">
         <v>13</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B46" s="9"/>
+      <c r="B46" s="10"/>
       <c r="C46" s="5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D46" s="5">
         <v>13</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="9"/>
+      <c r="B47" s="10"/>
       <c r="C47" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D47" s="5">
         <v>9</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="9"/>
+      <c r="B48" s="10"/>
       <c r="C48" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D48" s="5">
         <v>8</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B49" s="9"/>
+      <c r="B49" s="10"/>
       <c r="C49" s="5" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D49" s="5">
         <v>12</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B50" s="9"/>
+      <c r="B50" s="10"/>
       <c r="C50" s="5" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D50" s="5">
         <v>4</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B51" s="9"/>
+      <c r="B51" s="10"/>
       <c r="C51" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D51" s="5">
         <v>6</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B52" s="9"/>
+      <c r="B52" s="10"/>
       <c r="C52" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D52" s="5">
         <v>5</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B53" s="10"/>
+      <c r="B53" s="11"/>
       <c r="C53" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D53" s="5">
         <v>8</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="E53" s="5"/>
     </row>
     <row r="55" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
@@ -1292,248 +1239,208 @@
       <c r="E56" s="4"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B57" s="8" t="s">
-        <v>33</v>
+      <c r="B57" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D57" s="5">
         <v>11</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B58" s="9"/>
+      <c r="B58" s="10"/>
       <c r="C58" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D58" s="5">
         <v>13</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="9"/>
+      <c r="B59" s="10"/>
       <c r="C59" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D59" s="5">
         <v>14</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B60" s="9"/>
+      <c r="B60" s="10"/>
       <c r="C60" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D60" s="5">
         <v>6</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B61" s="9"/>
+      <c r="B61" s="10"/>
       <c r="C61" s="5" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D61" s="5">
         <v>6</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="E61" s="5"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B62" s="9"/>
+      <c r="B62" s="10"/>
       <c r="C62" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D62" s="5">
         <v>5</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B63" s="9"/>
+      <c r="B63" s="10"/>
       <c r="C63" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D63" s="5">
         <v>4</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="E63" s="5"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B64" s="10"/>
+      <c r="B64" s="11"/>
       <c r="C64" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D64" s="5">
         <v>10</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="E64" s="5"/>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B67" s="11" t="s">
-        <v>29</v>
+      <c r="B67" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D67" s="7">
         <v>4</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E67" s="5"/>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B68" s="12"/>
+      <c r="B68" s="13"/>
       <c r="C68" s="5" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D68" s="5">
         <v>4</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E68" s="5"/>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B69" s="12"/>
+      <c r="B69" s="13"/>
       <c r="C69" s="5" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D69" s="5">
         <v>7</v>
       </c>
-      <c r="E69" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E69" s="5"/>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B70" s="12"/>
+      <c r="B70" s="13"/>
       <c r="C70" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D70" s="5">
         <v>6</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E70" s="5"/>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B71" s="12"/>
+      <c r="B71" s="13"/>
       <c r="C71" s="5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D71" s="5">
         <v>8</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E71" s="5"/>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B72" s="12"/>
+      <c r="B72" s="13"/>
       <c r="C72" s="5" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D72" s="5">
         <v>8</v>
       </c>
-      <c r="E72" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E72" s="5"/>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B73" s="12"/>
+      <c r="B73" s="13"/>
       <c r="C73" s="5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D73" s="5">
         <v>3</v>
       </c>
-      <c r="E73" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E73" s="5"/>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B74" s="12"/>
-      <c r="C74" s="16" t="s">
-        <v>90</v>
+      <c r="B74" s="13"/>
+      <c r="C74" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="D74" s="5">
         <v>4</v>
       </c>
-      <c r="E74" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E74" s="5"/>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B75" s="12"/>
-      <c r="C75" s="16" t="s">
-        <v>88</v>
+      <c r="B75" s="13"/>
+      <c r="C75" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="D75" s="5">
         <v>3</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E75" s="5"/>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B76" s="12"/>
-      <c r="C76" s="16" t="s">
-        <v>87</v>
+      <c r="B76" s="13"/>
+      <c r="C76" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="D76" s="5">
         <v>3</v>
       </c>
-      <c r="E76" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E76" s="5"/>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B77" s="12"/>
-      <c r="C77" s="16" t="s">
-        <v>85</v>
+      <c r="B77" s="13"/>
+      <c r="C77" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="D77" s="5">
         <v>6</v>
       </c>
-      <c r="E77" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E77" s="5"/>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B78" s="12"/>
-      <c r="C78" s="16" t="s">
-        <v>92</v>
+      <c r="B78" s="13"/>
+      <c r="C78" s="8" t="s">
+        <v>82</v>
       </c>
       <c r="D78" s="5">
         <v>2</v>
       </c>
-      <c r="E78" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="E78" s="5"/>
     </row>
   </sheetData>
   <dataConsolidate>
